--- a/public/excluded-faculty.xlsx
+++ b/public/excluded-faculty.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="303">
   <si>
     <t>Emp ID</t>
   </si>
@@ -114,6 +114,12 @@
     <t>4554</t>
   </si>
   <si>
+    <t>SECETCS146</t>
+  </si>
+  <si>
+    <t>Sridharan S</t>
+  </si>
+  <si>
     <t>SECEPOP11</t>
   </si>
   <si>
@@ -339,6 +345,21 @@
     <t>6019</t>
   </si>
   <si>
+    <t>SECETCS0000</t>
+  </si>
+  <si>
+    <t>Anandakumar H - Dean</t>
+  </si>
+  <si>
+    <t>Professor &amp; Asst Dean</t>
+  </si>
+  <si>
+    <t>1/12</t>
+  </si>
+  <si>
+    <t>Dr Sudha Mohanram</t>
+  </si>
+  <si>
     <t>SECETCS145</t>
   </si>
   <si>
@@ -489,6 +510,30 @@
     <t>6022</t>
   </si>
   <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>College Maintenance</t>
+  </si>
+  <si>
+    <t>COLLEGE MAINTENANCE</t>
+  </si>
+  <si>
+    <t>cmain</t>
+  </si>
+  <si>
+    <t>SECEADM0001</t>
+  </si>
+  <si>
+    <t>IQAC Dean</t>
+  </si>
+  <si>
+    <t>IQAC</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
     <t>SECETEC101</t>
   </si>
   <si>
@@ -549,9 +594,6 @@
     <t>SECEPR001</t>
   </si>
   <si>
-    <t>Dr Sudha Mohanram</t>
-  </si>
-  <si>
     <t>principal1@sece.ac.in</t>
   </si>
   <si>
@@ -564,6 +606,30 @@
     <t>8090</t>
   </si>
   <si>
+    <t>electric</t>
+  </si>
+  <si>
+    <t>Electrical Maintenance</t>
+  </si>
+  <si>
+    <t>Electrical and Maintenance</t>
+  </si>
+  <si>
+    <t>emain</t>
+  </si>
+  <si>
+    <t>SECEIno006</t>
+  </si>
+  <si>
+    <t>Innovation Head</t>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>ino</t>
+  </si>
+  <si>
     <t>SECEPOP005</t>
   </si>
   <si>
@@ -810,6 +876,15 @@
     <t>2514</t>
   </si>
   <si>
+    <t>SECEADM9081</t>
+  </si>
+  <si>
+    <t>Student Welfare</t>
+  </si>
+  <si>
+    <t>student</t>
+  </si>
+  <si>
     <t>SECETCS134</t>
   </si>
   <si>
@@ -817,6 +892,36 @@
   </si>
   <si>
     <t>Subha</t>
+  </si>
+  <si>
+    <t>SECEDRI063</t>
+  </si>
+  <si>
+    <t>Natarajan R</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>SECEDRI00t</t>
+  </si>
+  <si>
+    <t>Transport T</t>
+  </si>
+  <si>
+    <t>270t</t>
+  </si>
+  <si>
+    <t>SECEFAB001</t>
+  </si>
+  <si>
+    <t>Mohanasundaram S</t>
+  </si>
+  <si>
+    <t>Electrical-Maintenance</t>
   </si>
 </sst>
 </file>
@@ -833,7 +938,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.0"/>
@@ -855,8 +959,22 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
     <border>
       <left/>
       <right/>
@@ -867,12 +985,33 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1100,7 +1239,6 @@
     <col customWidth="1" min="8" max="8" width="25.78"/>
     <col customWidth="1" min="9" max="9" width="12.78"/>
     <col customWidth="1" min="10" max="11" width="22.78"/>
-    <col customWidth="1" min="12" max="26" width="8.56"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -1247,64 +1385,58 @@
       <c r="A5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="4">
+        <v>7039.0</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>19</v>
@@ -1315,31 +1447,31 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>19</v>
@@ -1350,34 +1482,34 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="J8" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>20</v>
@@ -1385,34 +1517,34 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>20</v>
@@ -1420,34 +1552,34 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>20</v>
@@ -1455,34 +1587,34 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>20</v>
@@ -1490,34 +1622,34 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>20</v>
@@ -1525,34 +1657,34 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="E13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="J13" s="1" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>20</v>
@@ -1560,31 +1692,31 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>19</v>
@@ -1595,31 +1727,31 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>19</v>
@@ -1630,31 +1762,31 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>19</v>
@@ -1665,31 +1797,31 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>19</v>
@@ -1699,67 +1831,67 @@
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="G18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="I18" s="6">
+        <v>2009.0</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="E19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>19</v>
@@ -1770,31 +1902,31 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="E20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>19</v>
@@ -1805,31 +1937,31 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>19</v>
@@ -1840,31 +1972,31 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>19</v>
@@ -1875,31 +2007,31 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>19</v>
@@ -1910,31 +2042,31 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>19</v>
@@ -1945,31 +2077,31 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>19</v>
@@ -1979,32 +2111,32 @@
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>19</v>
@@ -2015,31 +2147,31 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>19</v>
@@ -2049,102 +2181,92 @@
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="J29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H28" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="1" t="s">
+      <c r="E30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="G30" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>19</v>
@@ -2155,31 +2277,31 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>194</v>
+        <v>151</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>19</v>
@@ -2190,31 +2312,31 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>19</v>
@@ -2225,31 +2347,31 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>19</v>
@@ -2259,102 +2381,90 @@
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" s="1" t="s">
+      <c r="A34" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" s="1" t="s">
+      <c r="A35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>19</v>
@@ -2364,137 +2474,137 @@
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="2" t="s">
-        <v>225</v>
+      <c r="A37" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>233</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>234</v>
+      <c r="A38" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>238</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>233</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>233</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>252</v>
+        <v>114</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>19</v>
@@ -2505,31 +2615,31 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>258</v>
+        <v>114</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>19</v>
@@ -2540,31 +2650,31 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>19</v>
@@ -2574,32 +2684,350 @@
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H43" s="1" t="s">
+      <c r="F45" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
+      <c r="K46" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="A47" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1">
+      <c r="A48" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="I51" s="9">
+        <v>2716.0</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" customHeight="1">
+      <c r="A52" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25" customHeight="1">
+      <c r="A53" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I53" s="9">
+        <v>3325.0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
     <row r="54" ht="14.25" customHeight="1"/>
     <row r="55" ht="14.25" customHeight="1"/>
     <row r="56" ht="14.25" customHeight="1"/>
@@ -2800,752 +3228,763 @@
     <row r="251" ht="14.25" customHeight="1"/>
     <row r="252" ht="14.25" customHeight="1"/>
     <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$A$1:$K$1">
     <sortState ref="A1:K1">
